--- a/data/nzd0117/nzd0117.xlsx
+++ b/data/nzd0117/nzd0117.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E245"/>
+  <dimension ref="A1:E246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5577,6 +5577,27 @@
         <v>332.51</v>
       </c>
       <c r="E245" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>380.87</v>
+      </c>
+      <c r="C246" t="n">
+        <v>313.17</v>
+      </c>
+      <c r="D246" t="n">
+        <v>329.05</v>
+      </c>
+      <c r="E246" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -5593,7 +5614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B297"/>
+  <dimension ref="A1:B298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8566,6 +8587,16 @@
       </c>
       <c r="B297" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -8734,28 +8765,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1915589610021073</v>
+        <v>-0.1892436185058507</v>
       </c>
       <c r="J2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01199504276871122</v>
+        <v>0.01181527526744752</v>
       </c>
       <c r="M2" t="n">
-        <v>9.856477888859553</v>
+        <v>9.826029819203116</v>
       </c>
       <c r="N2" t="n">
-        <v>163.4993688904085</v>
+        <v>162.86345322001</v>
       </c>
       <c r="O2" t="n">
-        <v>12.7866871741827</v>
+        <v>12.76179662978571</v>
       </c>
       <c r="P2" t="n">
-        <v>383.2087399017633</v>
+        <v>383.1836345109167</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8812,28 +8843,28 @@
         <v>0.0653</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2726458670786591</v>
+        <v>0.2566167516137742</v>
       </c>
       <c r="J3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05559217618833301</v>
+        <v>0.04896881553926202</v>
       </c>
       <c r="M3" t="n">
-        <v>6.41939344811637</v>
+        <v>6.444381414758939</v>
       </c>
       <c r="N3" t="n">
-        <v>68.31208657430011</v>
+        <v>69.53957375031987</v>
       </c>
       <c r="O3" t="n">
-        <v>8.265112617157742</v>
+        <v>8.339039138313231</v>
       </c>
       <c r="P3" t="n">
-        <v>325.1995954267392</v>
+        <v>325.373400040666</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8890,28 +8921,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.005201390877403432</v>
+        <v>-0.01353187167711045</v>
       </c>
       <c r="J4" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K4" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L4" t="n">
-        <v>3.252126343866735e-05</v>
+        <v>0.0002201137423427646</v>
       </c>
       <c r="M4" t="n">
-        <v>5.098991135302352</v>
+        <v>5.114026421828582</v>
       </c>
       <c r="N4" t="n">
-        <v>44.99987029512145</v>
+        <v>45.22304889332437</v>
       </c>
       <c r="O4" t="n">
-        <v>6.708194264861554</v>
+        <v>6.724808465177604</v>
       </c>
       <c r="P4" t="n">
-        <v>339.2400862977659</v>
+        <v>339.3304141765806</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8949,7 +8980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E245"/>
+  <dimension ref="A1:E246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15567,6 +15598,33 @@
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>-36.15190565857146,175.44679584745745</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>-36.152713413840566,175.447428150937</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>-36.15280155735118,175.4483342203881</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0117/nzd0117.xlsx
+++ b/data/nzd0117/nzd0117.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E246"/>
+  <dimension ref="A1:E247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5600,6 +5600,27 @@
       <c r="E246" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>389.13</v>
+      </c>
+      <c r="C247" t="n">
+        <v>315.78</v>
+      </c>
+      <c r="D247" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B298"/>
+  <dimension ref="A1:B299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8597,6 +8618,16 @@
       </c>
       <c r="B298" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -8765,28 +8796,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1892436185058507</v>
+        <v>-0.1802102332299525</v>
       </c>
       <c r="J2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01181527526744752</v>
+        <v>0.01079104150637877</v>
       </c>
       <c r="M2" t="n">
-        <v>9.826029819203116</v>
+        <v>9.824017829070485</v>
       </c>
       <c r="N2" t="n">
-        <v>162.86345322001</v>
+        <v>162.6887300135331</v>
       </c>
       <c r="O2" t="n">
-        <v>12.76179662978571</v>
+        <v>12.75494923602337</v>
       </c>
       <c r="P2" t="n">
-        <v>383.1836345109167</v>
+        <v>383.0855969307526</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8843,28 +8874,28 @@
         <v>0.0653</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2566167516137742</v>
+        <v>0.2431091619589598</v>
       </c>
       <c r="J3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04896881553926202</v>
+        <v>0.04389737338784794</v>
       </c>
       <c r="M3" t="n">
-        <v>6.444381414758939</v>
+        <v>6.464034427221248</v>
       </c>
       <c r="N3" t="n">
-        <v>69.53957375031987</v>
+        <v>70.34650454489991</v>
       </c>
       <c r="O3" t="n">
-        <v>8.339039138313231</v>
+        <v>8.387282309836715</v>
       </c>
       <c r="P3" t="n">
-        <v>325.373400040666</v>
+        <v>325.5199952940692</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8921,28 +8952,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01353187167711045</v>
+        <v>-0.01932439642985166</v>
       </c>
       <c r="J4" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K4" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002201137423427646</v>
+        <v>0.0004508906251743383</v>
       </c>
       <c r="M4" t="n">
-        <v>5.114026421828582</v>
+        <v>5.11800704910925</v>
       </c>
       <c r="N4" t="n">
-        <v>45.22304889332437</v>
+        <v>45.23959424456288</v>
       </c>
       <c r="O4" t="n">
-        <v>6.724808465177604</v>
+        <v>6.726038525355239</v>
       </c>
       <c r="P4" t="n">
-        <v>339.3304141765806</v>
+        <v>339.3932793254097</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8980,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E246"/>
+  <dimension ref="A1:E247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15625,6 +15656,33 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>-36.15183454123563,175.44682290298886</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>-36.15269094212322,175.44743669994284</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>-36.15277701923259,175.4483435553253</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0117/nzd0117.xlsx
+++ b/data/nzd0117/nzd0117.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E247"/>
+  <dimension ref="A1:E248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5621,6 +5621,27 @@
       <c r="E247" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>388.94</v>
+      </c>
+      <c r="C248" t="n">
+        <v>314.71</v>
+      </c>
+      <c r="D248" t="n">
+        <v>331.27</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B299"/>
+  <dimension ref="A1:B300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8628,6 +8649,16 @@
       </c>
       <c r="B299" t="n">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -8796,28 +8827,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1802102332299525</v>
+        <v>-0.1714631947616433</v>
       </c>
       <c r="J2" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K2" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01079104150637877</v>
+        <v>0.009840191476408466</v>
       </c>
       <c r="M2" t="n">
-        <v>9.824017829070485</v>
+        <v>9.820498893576028</v>
       </c>
       <c r="N2" t="n">
-        <v>162.6887300135331</v>
+        <v>162.4881487017919</v>
       </c>
       <c r="O2" t="n">
-        <v>12.75494923602337</v>
+        <v>12.74708392934603</v>
       </c>
       <c r="P2" t="n">
-        <v>383.0855969307526</v>
+        <v>382.9902400760409</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8874,28 +8905,28 @@
         <v>0.0653</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2431091619589598</v>
+        <v>0.2289319652442313</v>
       </c>
       <c r="J3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04389737338784794</v>
+        <v>0.03882545564799866</v>
       </c>
       <c r="M3" t="n">
-        <v>6.464034427221248</v>
+        <v>6.48954323577382</v>
       </c>
       <c r="N3" t="n">
-        <v>70.34650454489991</v>
+        <v>71.26506659206584</v>
       </c>
       <c r="O3" t="n">
-        <v>8.387282309836715</v>
+        <v>8.441863928781714</v>
       </c>
       <c r="P3" t="n">
-        <v>325.5199952940692</v>
+        <v>325.6745496489224</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8952,28 +8983,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01932439642985166</v>
+        <v>-0.02553353091688518</v>
       </c>
       <c r="J4" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K4" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004508906251743383</v>
+        <v>0.0007900972478703805</v>
       </c>
       <c r="M4" t="n">
-        <v>5.11800704910925</v>
+        <v>5.123548419037235</v>
       </c>
       <c r="N4" t="n">
-        <v>45.23959424456288</v>
+        <v>45.28726096751065</v>
       </c>
       <c r="O4" t="n">
-        <v>6.726038525355239</v>
+        <v>6.729581039523238</v>
       </c>
       <c r="P4" t="n">
-        <v>339.3932793254097</v>
+        <v>339.4609689254167</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -9011,7 +9042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E247"/>
+  <dimension ref="A1:E248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15683,6 +15714,33 @@
         </is>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>-36.15183617710662,175.44682228064664</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>-36.15270015466642,175.44743319517855</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>-36.15278244344833,175.44834149181335</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
